--- a/e-PACS/target/test-classes/TestData/TestData.xlsx
+++ b/e-PACS/target/test-classes/TestData/TestData.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aa\e-PACS\src\test\resources\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\ERPAUTOMATION\e-PACS\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{457AC7DA-7A8B-426B-9865-E18D4B05BD61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050AFC9C-BE98-4933-B3FB-62FDAF7E1DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA73783C-BD21-40DB-ADE3-1F3CA440F980}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TestData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -24,15 +24,44 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>New Admission</t>
+  </si>
+  <si>
+    <t>CustomerType</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>0103961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Village </t>
+  </si>
+  <si>
+    <t>padghe</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,8 +84,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -75,9 +105,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -115,7 +145,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -221,7 +251,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -363,7 +393,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -371,9 +401,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8457BC02-1D6B-4BEC-95E7-04DCBF926EFB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>